--- a/output_data/charts/0500000US39141.xlsx
+++ b/output_data/charts/0500000US39141.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.3969168523213235</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>0.5351572187487763</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.4918947682643513</c:v>
+                  <c:v>0.4917734987283957</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4954248366013072</c:v>
+                  <c:v>0.4939497687060607</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.5084435614576254</c:v>
+                  <c:v>0.5060212607382418</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.5477052587547876</c:v>
+                  <c:v>0.5383809274299188</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.5509823001867291</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>6.200865534813449</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>5.574771905551277</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.578268374670664</c:v>
+                  <c:v>5.585976021176104</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.50718954248366</c:v>
+                  <c:v>5.518385908057392</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.636011920322058</c:v>
+                  <c:v>5.655147164581127</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.633913282179318</c:v>
+                  <c:v>5.648414985590778</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.662362254424953</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.9730864766587284</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>1.388798245728532</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.367960648418539</c:v>
+                  <c:v>1.366325842113458</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.339869281045752</c:v>
+                  <c:v>1.342027546193451</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.436451090082083</c:v>
+                  <c:v>1.438303325095778</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.477104874446086</c:v>
+                  <c:v>1.480220068116322</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.509612602898246</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.2765614196819544</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.3367574693589861</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.3283624706355696</c:v>
+                  <c:v>0.3295790730264182</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.334640522875817</c:v>
+                  <c:v>0.3358335729033269</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.35682543002039</c:v>
+                  <c:v>0.3608833797513042</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.3647011150181043</c:v>
+                  <c:v>0.3628504060780718</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.3734581700549667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.938490691659625</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>2.560923080939266</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.629495515840569</c:v>
+                  <c:v>2.627549696372035</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.632679738562091</c:v>
+                  <c:v>2.630478530172752</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.70559941444032</c:v>
+                  <c:v>2.701395154225343</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.836564227918589</c:v>
+                  <c:v>2.825517422059209</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.781211372064277</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>90.21407902486493</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>89.60359207967316</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>89.60401822217031</c:v>
+                  <c:v>89.59879586858359</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>89.69019607843137</c:v>
+                  <c:v>89.67932467396702</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>89.35666858367752</c:v>
+                  <c:v>89.33824971560821</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>89.14001124168311</c:v>
+                  <c:v>89.1446161907257</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>89.12237330037082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>0.4918947682643513</v>
+        <v>0.4917734987283957</v>
       </c>
       <c r="C12" s="2">
-        <v>5.578268374670664</v>
+        <v>5.585976021176104</v>
       </c>
       <c r="D12" s="2">
-        <v>1.367960648418539</v>
+        <v>1.366325842113458</v>
       </c>
       <c r="E12" s="2">
-        <v>0.3283624706355696</v>
+        <v>0.3295790730264182</v>
       </c>
       <c r="F12" s="2">
-        <v>2.629495515840569</v>
+        <v>2.627549696372035</v>
       </c>
       <c r="G12" s="2">
-        <v>89.60401822217031</v>
+        <v>89.59879586858359</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>0.4954248366013072</v>
+        <v>0.4939497687060607</v>
       </c>
       <c r="C13" s="2">
-        <v>5.50718954248366</v>
+        <v>5.518385908057392</v>
       </c>
       <c r="D13" s="2">
-        <v>1.339869281045752</v>
+        <v>1.342027546193451</v>
       </c>
       <c r="E13" s="2">
-        <v>0.334640522875817</v>
+        <v>0.3358335729033269</v>
       </c>
       <c r="F13" s="2">
-        <v>2.632679738562091</v>
+        <v>2.630478530172752</v>
       </c>
       <c r="G13" s="2">
-        <v>89.69019607843137</v>
+        <v>89.67932467396702</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>0.5084435614576254</v>
+        <v>0.5060212607382418</v>
       </c>
       <c r="C14" s="2">
-        <v>5.636011920322058</v>
+        <v>5.655147164581127</v>
       </c>
       <c r="D14" s="2">
-        <v>1.436451090082083</v>
+        <v>1.438303325095778</v>
       </c>
       <c r="E14" s="2">
-        <v>0.35682543002039</v>
+        <v>0.3608833797513042</v>
       </c>
       <c r="F14" s="2">
-        <v>2.70559941444032</v>
+        <v>2.701395154225343</v>
       </c>
       <c r="G14" s="2">
-        <v>89.35666858367752</v>
+        <v>89.33824971560821</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>0.5477052587547876</v>
+        <v>0.5383809274299188</v>
       </c>
       <c r="C15" s="2">
-        <v>5.633913282179318</v>
+        <v>5.648414985590778</v>
       </c>
       <c r="D15" s="2">
-        <v>1.477104874446086</v>
+        <v>1.480220068116322</v>
       </c>
       <c r="E15" s="2">
-        <v>0.3647011150181043</v>
+        <v>0.3628504060780718</v>
       </c>
       <c r="F15" s="2">
-        <v>2.836564227918589</v>
+        <v>2.825517422059209</v>
       </c>
       <c r="G15" s="2">
-        <v>89.14001124168311</v>
+        <v>89.1446161907257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.5509823001867291</v>
+      </c>
+      <c r="C16" s="2">
+        <v>5.662362254424953</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1.509612602898246</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.3734581700549667</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2.781211372064277</v>
+      </c>
+      <c r="G16" s="2">
+        <v>89.12237330037082</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39141.xlsx
+++ b/output_data/charts/0500000US39141.xlsx
@@ -226,34 +226,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.3969168523213235</c:v>
+                  <c:v>0.3982176240108582</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.421424336933268</c:v>
+                  <c:v>0.4202059782678748</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4252898822373609</c:v>
+                  <c:v>0.4215099365149144</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.4734860735585195</c:v>
+                  <c:v>0.469702263110904</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.4849836609782665</c:v>
+                  <c:v>0.4799273623451586</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.5164337524491677</c:v>
+                  <c:v>0.5087671481784319</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.517636042035168</c:v>
+                  <c:v>0.5140016656256506</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.507121696270327</c:v>
+                  <c:v>0.5162041529206287</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.5425519457708271</c:v>
+                  <c:v>0.5592841163310962</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.5351572187487763</c:v>
+                  <c:v>0.5491352098713902</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.4917734987283957</c:v>
@@ -357,34 +357,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>6.200865534813449</c:v>
+                  <c:v>6.198622243847474</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.048148052684486</c:v>
+                  <c:v>6.038849718358877</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.921741490970669</c:v>
+                  <c:v>5.906311012270335</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.878471907786647</c:v>
+                  <c:v>5.864161587930075</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.904092535919913</c:v>
+                  <c:v>5.874570335300603</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.82090907911298</c:v>
+                  <c:v>5.798907188931719</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.831859327853501</c:v>
+                  <c:v>5.806266916510515</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.031125887786388</c:v>
+                  <c:v>6.004269357655734</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.739080654184936</c:v>
+                  <c:v>5.726809219083295</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.574771905551277</c:v>
+                  <c:v>5.53178723293246</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>5.585976021176104</c:v>
@@ -488,34 +488,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.9730864766587284</c:v>
+                  <c:v>0.9744167584317139</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.063226538134392</c:v>
+                  <c:v>1.068560601178123</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.097480577566928</c:v>
+                  <c:v>1.10420087663723</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.098332449320172</c:v>
+                  <c:v>1.105029566657609</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.147621764614347</c:v>
+                  <c:v>1.157014073545625</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.153541723435452</c:v>
+                  <c:v>1.165492089449571</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.210852148579753</c:v>
+                  <c:v>1.228398917343327</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.261335851692778</c:v>
+                  <c:v>1.261401125557927</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.328406562666701</c:v>
+                  <c:v>1.325373289631133</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.388798245728532</c:v>
+                  <c:v>1.38262071844103</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.366325842113458</c:v>
@@ -619,34 +619,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.2765614196819544</c:v>
+                  <c:v>0.2765755845220108</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.280949557955512</c:v>
+                  <c:v>0.2809966357742231</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2805103478586848</c:v>
+                  <c:v>0.2818686078535317</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2897838264401869</c:v>
+                  <c:v>0.2911377663910563</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2982519840240677</c:v>
+                  <c:v>0.2996303262208963</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3049294769486291</c:v>
+                  <c:v>0.3062985892094641</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.312142336905629</c:v>
+                  <c:v>0.3149073495731834</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3040142822028745</c:v>
+                  <c:v>0.3066175043663885</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3109590288710496</c:v>
+                  <c:v>0.3082565943499297</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3367574693589861</c:v>
+                  <c:v>0.3286985104218298</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.3295790730264182</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.938490691659625</c:v>
+                  <c:v>1.938589976695946</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.028507358816403</c:v>
+                  <c:v>2.027558293912169</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.079913132279373</c:v>
+                  <c:v>2.077811251470759</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.168203987114969</c:v>
+                  <c:v>2.164771036321054</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.186316717672078</c:v>
+                  <c:v>2.185615150139439</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.252585412692852</c:v>
+                  <c:v>2.246622279328739</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.318957444594735</c:v>
+                  <c:v>2.312356860295648</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.389422890334933</c:v>
+                  <c:v>2.394721521443819</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.421316957025202</c:v>
+                  <c:v>2.41792830758025</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.560923080939266</c:v>
+                  <c:v>2.551326533274203</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.627549696372035</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>90.21407902486493</c:v>
+                  <c:v>90.21357781249199</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90.15774415547594</c:v>
+                  <c:v>90.16382877250874</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>90.19506456908698</c:v>
+                  <c:v>90.20829831525323</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90.0917217557795</c:v>
+                  <c:v>90.1051977795893</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>89.97873333679132</c:v>
+                  <c:v>90.00324275244827</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>89.95160055536093</c:v>
+                  <c:v>89.97391270490208</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>89.80855270003121</c:v>
+                  <c:v>89.82406829065167</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>89.5069793917127</c:v>
+                  <c:v>89.5167863380555</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>89.65768485148128</c:v>
+                  <c:v>89.6623484730243</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>89.60359207967316</c:v>
+                  <c:v>89.65643179505909</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>89.59879586858359</c:v>
@@ -1396,22 +1396,22 @@
         <v>2010</v>
       </c>
       <c r="B2" s="2">
-        <v>0.3969168523213235</v>
+        <v>0.3982176240108582</v>
       </c>
       <c r="C2" s="2">
-        <v>6.200865534813449</v>
+        <v>6.198622243847474</v>
       </c>
       <c r="D2" s="2">
-        <v>0.9730864766587284</v>
+        <v>0.9744167584317139</v>
       </c>
       <c r="E2" s="2">
-        <v>0.2765614196819544</v>
+        <v>0.2765755845220108</v>
       </c>
       <c r="F2" s="2">
-        <v>1.938490691659625</v>
+        <v>1.938589976695946</v>
       </c>
       <c r="G2" s="2">
-        <v>90.21407902486493</v>
+        <v>90.21357781249199</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>0.421424336933268</v>
+        <v>0.4202059782678748</v>
       </c>
       <c r="C3" s="2">
-        <v>6.048148052684486</v>
+        <v>6.038849718358877</v>
       </c>
       <c r="D3" s="2">
-        <v>1.063226538134392</v>
+        <v>1.068560601178123</v>
       </c>
       <c r="E3" s="2">
-        <v>0.280949557955512</v>
+        <v>0.2809966357742231</v>
       </c>
       <c r="F3" s="2">
-        <v>2.028507358816403</v>
+        <v>2.027558293912169</v>
       </c>
       <c r="G3" s="2">
-        <v>90.15774415547594</v>
+        <v>90.16382877250874</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>0.4252898822373609</v>
+        <v>0.4215099365149144</v>
       </c>
       <c r="C4" s="2">
-        <v>5.921741490970669</v>
+        <v>5.906311012270335</v>
       </c>
       <c r="D4" s="2">
-        <v>1.097480577566928</v>
+        <v>1.10420087663723</v>
       </c>
       <c r="E4" s="2">
-        <v>0.2805103478586848</v>
+        <v>0.2818686078535317</v>
       </c>
       <c r="F4" s="2">
-        <v>2.079913132279373</v>
+        <v>2.077811251470759</v>
       </c>
       <c r="G4" s="2">
-        <v>90.19506456908698</v>
+        <v>90.20829831525323</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>0.4734860735585195</v>
+        <v>0.469702263110904</v>
       </c>
       <c r="C5" s="2">
-        <v>5.878471907786647</v>
+        <v>5.864161587930075</v>
       </c>
       <c r="D5" s="2">
-        <v>1.098332449320172</v>
+        <v>1.105029566657609</v>
       </c>
       <c r="E5" s="2">
-        <v>0.2897838264401869</v>
+        <v>0.2911377663910563</v>
       </c>
       <c r="F5" s="2">
-        <v>2.168203987114969</v>
+        <v>2.164771036321054</v>
       </c>
       <c r="G5" s="2">
-        <v>90.0917217557795</v>
+        <v>90.1051977795893</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>0.4849836609782665</v>
+        <v>0.4799273623451586</v>
       </c>
       <c r="C6" s="2">
-        <v>5.904092535919913</v>
+        <v>5.874570335300603</v>
       </c>
       <c r="D6" s="2">
-        <v>1.147621764614347</v>
+        <v>1.157014073545625</v>
       </c>
       <c r="E6" s="2">
-        <v>0.2982519840240677</v>
+        <v>0.2996303262208963</v>
       </c>
       <c r="F6" s="2">
-        <v>2.186316717672078</v>
+        <v>2.185615150139439</v>
       </c>
       <c r="G6" s="2">
-        <v>89.97873333679132</v>
+        <v>90.00324275244827</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>0.5164337524491677</v>
+        <v>0.5087671481784319</v>
       </c>
       <c r="C7" s="2">
-        <v>5.82090907911298</v>
+        <v>5.798907188931719</v>
       </c>
       <c r="D7" s="2">
-        <v>1.153541723435452</v>
+        <v>1.165492089449571</v>
       </c>
       <c r="E7" s="2">
-        <v>0.3049294769486291</v>
+        <v>0.3062985892094641</v>
       </c>
       <c r="F7" s="2">
-        <v>2.252585412692852</v>
+        <v>2.246622279328739</v>
       </c>
       <c r="G7" s="2">
-        <v>89.95160055536093</v>
+        <v>89.97391270490208</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>0.517636042035168</v>
+        <v>0.5140016656256506</v>
       </c>
       <c r="C8" s="2">
-        <v>5.831859327853501</v>
+        <v>5.806266916510515</v>
       </c>
       <c r="D8" s="2">
-        <v>1.210852148579753</v>
+        <v>1.228398917343327</v>
       </c>
       <c r="E8" s="2">
-        <v>0.312142336905629</v>
+        <v>0.3149073495731834</v>
       </c>
       <c r="F8" s="2">
-        <v>2.318957444594735</v>
+        <v>2.312356860295648</v>
       </c>
       <c r="G8" s="2">
-        <v>89.80855270003121</v>
+        <v>89.82406829065167</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>0.507121696270327</v>
+        <v>0.5162041529206287</v>
       </c>
       <c r="C9" s="2">
-        <v>6.031125887786388</v>
+        <v>6.004269357655734</v>
       </c>
       <c r="D9" s="2">
-        <v>1.261335851692778</v>
+        <v>1.261401125557927</v>
       </c>
       <c r="E9" s="2">
-        <v>0.3040142822028745</v>
+        <v>0.3066175043663885</v>
       </c>
       <c r="F9" s="2">
-        <v>2.389422890334933</v>
+        <v>2.394721521443819</v>
       </c>
       <c r="G9" s="2">
-        <v>89.5069793917127</v>
+        <v>89.5167863380555</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>0.5425519457708271</v>
+        <v>0.5592841163310962</v>
       </c>
       <c r="C10" s="2">
-        <v>5.739080654184936</v>
+        <v>5.726809219083295</v>
       </c>
       <c r="D10" s="2">
-        <v>1.328406562666701</v>
+        <v>1.325373289631133</v>
       </c>
       <c r="E10" s="2">
-        <v>0.3109590288710496</v>
+        <v>0.3082565943499297</v>
       </c>
       <c r="F10" s="2">
-        <v>2.421316957025202</v>
+        <v>2.41792830758025</v>
       </c>
       <c r="G10" s="2">
-        <v>89.65768485148128</v>
+        <v>89.6623484730243</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>0.5351572187487763</v>
+        <v>0.5491352098713902</v>
       </c>
       <c r="C11" s="2">
-        <v>5.574771905551277</v>
+        <v>5.53178723293246</v>
       </c>
       <c r="D11" s="2">
-        <v>1.388798245728532</v>
+        <v>1.38262071844103</v>
       </c>
       <c r="E11" s="2">
-        <v>0.3367574693589861</v>
+        <v>0.3286985104218298</v>
       </c>
       <c r="F11" s="2">
-        <v>2.560923080939266</v>
+        <v>2.551326533274203</v>
       </c>
       <c r="G11" s="2">
-        <v>89.60359207967316</v>
+        <v>89.65643179505909</v>
       </c>
     </row>
     <row r="12" spans="1:7">
